--- a/artfynd/A 49421-2023 artfynd.xlsx
+++ b/artfynd/A 49421-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122034579</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2023 artfynd.xlsx
+++ b/artfynd/A 49421-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034579</v>
+        <v>119347623</v>
       </c>
       <c r="B2" t="n">
-        <v>58024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björksättra, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670441</v>
+        <v>670503</v>
       </c>
       <c r="R2" t="n">
-        <v>6562435</v>
+        <v>6562512</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,17 +760,546 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jörgen Wissman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jörgen Wissman, Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>ESN0033 Björksättra NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122034579</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>670441</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562435</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Marlijn Sterenborg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Edwin Sahlin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122034681</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>670464</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6562437</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På håll, osäker på exakt punkt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marie Björklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119347618</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>670504</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6562505</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Wissman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Wissman, Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ESN0033 Björksättra NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>75362544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gladö kvarns avfallsanläggning, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>670538</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6562498</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-07-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-07-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På åkervädd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119347619</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>670496</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6562500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Wissman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Wissman, Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 49421-2023 artfynd.xlsx
+++ b/artfynd/A 49421-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119347623</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034579</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
           <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119347618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75362544</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,8 +1332,21 @@
           <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119347619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>